--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N122_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N122_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.32709339127659</v>
+        <v>3.303152676082447</v>
       </c>
       <c r="D2" t="n">
-        <v>9.990208590107013</v>
+        <v>1.62340889589239</v>
       </c>
       <c r="E2" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F2" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.591339294577</v>
+        <v>4.483592635368762</v>
       </c>
       <c r="D3" t="n">
-        <v>31.64917718193455</v>
+        <v>5.142991292064365</v>
       </c>
       <c r="E3" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F3" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.13773830444201</v>
+        <v>3.597382474471826</v>
       </c>
       <c r="D4" t="n">
-        <v>23.86480902791808</v>
+        <v>3.878031467036688</v>
       </c>
       <c r="E4" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F4" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.572377789065103</v>
+        <v>1.230511390723079</v>
       </c>
       <c r="D5" t="n">
-        <v>28.11446973521616</v>
+        <v>4.568601331972626</v>
       </c>
       <c r="E5" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F5" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.55027920593308</v>
+        <v>8.376920370964125</v>
       </c>
       <c r="D6" t="n">
-        <v>44.5588695676903</v>
+        <v>7.240816304749674</v>
       </c>
       <c r="E6" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F6" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.45187380825684</v>
+        <v>9.498429493841737</v>
       </c>
       <c r="D7" t="n">
-        <v>54.75926806848919</v>
+        <v>8.898381061129493</v>
       </c>
       <c r="E7" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F7" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.96692897904755</v>
+        <v>4.382125959095227</v>
       </c>
       <c r="D8" t="n">
-        <v>19.47383630051117</v>
+        <v>3.164498398833066</v>
       </c>
       <c r="E8" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F8" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>57.37003515572846</v>
+        <v>9.322630712805875</v>
       </c>
       <c r="D9" t="n">
-        <v>42.83211582384926</v>
+        <v>6.960218821375505</v>
       </c>
       <c r="E9" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F9" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.65096935397312</v>
+        <v>2.543282520020633</v>
       </c>
       <c r="D10" t="n">
-        <v>6.725079701949082</v>
+        <v>1.092825451566726</v>
       </c>
       <c r="E10" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F10" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.261383328319707</v>
+        <v>1.017474790851952</v>
       </c>
       <c r="D11" t="n">
-        <v>4.68083615388613</v>
+        <v>0.7606358750064961</v>
       </c>
       <c r="E11" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F11" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>6.515744100573619</v>
+        <v>1.058808416343213</v>
       </c>
       <c r="D12" t="n">
-        <v>6.758408020498133</v>
+        <v>1.098241303330947</v>
       </c>
       <c r="E12" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F12" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.0224898367486</v>
+        <v>4.066154598471647</v>
       </c>
       <c r="D13" t="n">
-        <v>24.4923574605191</v>
+        <v>3.980008087334354</v>
       </c>
       <c r="E13" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F13" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.92788077148163</v>
+        <v>3.400780625365766</v>
       </c>
       <c r="D14" t="n">
-        <v>20.50059437705433</v>
+        <v>3.331346586271329</v>
       </c>
       <c r="E14" t="n">
-        <v>17.49250116735373</v>
+        <v>2.842531439694981</v>
       </c>
       <c r="F14" t="n">
-        <v>15.17571099023014</v>
+        <v>2.466053035912397</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
